--- a/02.06.2026/optimizationMethods/2_Lab_Tables.xlsx
+++ b/02.06.2026/optimizationMethods/2_Lab_Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbtw/Study/vyatsu_works/02.06.2026/optimizationMethods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{705E98CE-1321-4846-89A4-A3F5B3FD8AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7FE7FA-44DE-6841-9B46-D55149949F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4540" yWindow="600" windowWidth="22620" windowHeight="17400" firstSheet="3" activeTab="14" xr2:uid="{6D20C8F7-C5D0-E547-95CC-0B22E5C67ABC}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30360" windowHeight="17400" firstSheet="12" activeTab="26" xr2:uid="{6D20C8F7-C5D0-E547-95CC-0B22E5C67ABC}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,18 @@
     <sheet name="5" sheetId="17" r:id="rId13"/>
     <sheet name="5_1" sheetId="18" r:id="rId14"/>
     <sheet name="5_2" sheetId="19" r:id="rId15"/>
+    <sheet name="6" sheetId="20" r:id="rId16"/>
+    <sheet name="6_1" sheetId="21" r:id="rId17"/>
+    <sheet name="6_2" sheetId="22" r:id="rId18"/>
+    <sheet name="7" sheetId="23" r:id="rId19"/>
+    <sheet name="7_1" sheetId="24" r:id="rId20"/>
+    <sheet name="7_2" sheetId="25" r:id="rId21"/>
+    <sheet name="8" sheetId="26" r:id="rId22"/>
+    <sheet name="8_1" sheetId="27" r:id="rId23"/>
+    <sheet name="8_2" sheetId="28" r:id="rId24"/>
+    <sheet name="9" sheetId="29" r:id="rId25"/>
+    <sheet name="9_1" sheetId="30" r:id="rId26"/>
+    <sheet name="9_2" sheetId="31" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'1'!$B$2:$C$2</definedName>
@@ -35,172 +47,327 @@
     <definedName name="solver_adj" localSheetId="6" hidden="1">'3'!$B$2:$H$2</definedName>
     <definedName name="solver_adj" localSheetId="9" hidden="1">'4'!$B$2:$D$2</definedName>
     <definedName name="solver_adj" localSheetId="12" hidden="1">'5'!$B$2:$E$2</definedName>
+    <definedName name="solver_adj" localSheetId="15" hidden="1">'6'!$B$2:$E$2</definedName>
+    <definedName name="solver_adj" localSheetId="18" hidden="1">'7'!$B$2:$D$2</definedName>
+    <definedName name="solver_adj" localSheetId="21" hidden="1">'8'!$B$2:$D$2</definedName>
+    <definedName name="solver_adj" localSheetId="24" hidden="1">'9'!$B$2:$E$2</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="6" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="9" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="12" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="15" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="18" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="21" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="24" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="18" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="24" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="12" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="15" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="18" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="21" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="24" hidden="1">2</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="12" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="15" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="18" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="21" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="24" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'1'!$B$2:$C$2</definedName>
     <definedName name="solver_lhs1" localSheetId="3" hidden="1">'2'!$D$3:$D$5</definedName>
     <definedName name="solver_lhs1" localSheetId="6" hidden="1">'3'!$B$2:$H$2</definedName>
     <definedName name="solver_lhs1" localSheetId="9" hidden="1">'4'!$B$2:$D$2</definedName>
     <definedName name="solver_lhs1" localSheetId="12" hidden="1">'5'!$B$2:$E$2</definedName>
+    <definedName name="solver_lhs1" localSheetId="15" hidden="1">'6'!$B$2:$E$2</definedName>
+    <definedName name="solver_lhs1" localSheetId="18" hidden="1">'7'!$B$2</definedName>
+    <definedName name="solver_lhs1" localSheetId="21" hidden="1">'8'!$B$2:$D$2</definedName>
+    <definedName name="solver_lhs1" localSheetId="24" hidden="1">'9'!$B$2</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">'1'!$D$3:$D$5</definedName>
     <definedName name="solver_lhs2" localSheetId="3" hidden="1">'2'!$D$3:$D$5</definedName>
     <definedName name="solver_lhs2" localSheetId="6" hidden="1">'3'!$I$3:$I$6</definedName>
     <definedName name="solver_lhs2" localSheetId="9" hidden="1">'4'!$E$3:$E$5</definedName>
     <definedName name="solver_lhs2" localSheetId="12" hidden="1">'5'!$F$3:$F$4</definedName>
+    <definedName name="solver_lhs2" localSheetId="15" hidden="1">'6'!$F$3:$F$5</definedName>
+    <definedName name="solver_lhs2" localSheetId="18" hidden="1">'7'!$B$2</definedName>
+    <definedName name="solver_lhs2" localSheetId="21" hidden="1">'8'!$E$3:$E$5</definedName>
+    <definedName name="solver_lhs2" localSheetId="24" hidden="1">'9'!$C$2</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">'1'!$D$3:$D$5</definedName>
     <definedName name="solver_lhs3" localSheetId="3" hidden="1">'2'!$D$3:$D$5</definedName>
     <definedName name="solver_lhs3" localSheetId="9" hidden="1">'4'!$E$3:$E$5</definedName>
+    <definedName name="solver_lhs3" localSheetId="18" hidden="1">'7'!$C$2</definedName>
+    <definedName name="solver_lhs3" localSheetId="24" hidden="1">'9'!$D$2</definedName>
+    <definedName name="solver_lhs4" localSheetId="18" hidden="1">'7'!$C$2</definedName>
+    <definedName name="solver_lhs4" localSheetId="24" hidden="1">'9'!$E$2</definedName>
+    <definedName name="solver_lhs5" localSheetId="18" hidden="1">'7'!$D$2</definedName>
+    <definedName name="solver_lhs5" localSheetId="24" hidden="1">'9'!$F$3:$F$6</definedName>
+    <definedName name="solver_lhs6" localSheetId="18" hidden="1">'7'!$D$2</definedName>
+    <definedName name="solver_lhs6" localSheetId="24" hidden="1">'9'!$F$7</definedName>
+    <definedName name="solver_lhs7" localSheetId="18" hidden="1">'7'!$E$3:$E$6</definedName>
     <definedName name="solver_lin" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_lin" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_lin" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_lin" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_lin" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_lin" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_lin" localSheetId="18" hidden="1">1</definedName>
+    <definedName name="solver_lin" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_lin" localSheetId="24" hidden="1">1</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="12" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="15" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="18" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="21" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="24" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="3" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="6" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="9" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="12" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="15" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="18" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="21" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="24" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="3" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="6" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="9" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="12" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="15" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="18" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="21" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="24" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="12" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="15" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="18" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="21" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="24" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="18" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="24" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="12" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="15" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="18" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="21" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="24" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="12" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="15" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="18" hidden="1">7</definedName>
+    <definedName name="solver_num" localSheetId="21" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="24" hidden="1">6</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'1'!$D$6</definedName>
     <definedName name="solver_opt" localSheetId="3" hidden="1">'2'!$D$6</definedName>
     <definedName name="solver_opt" localSheetId="6" hidden="1">'3'!$I$7</definedName>
     <definedName name="solver_opt" localSheetId="9" hidden="1">'4'!$E$6</definedName>
     <definedName name="solver_opt" localSheetId="12" hidden="1">'5'!$F$5</definedName>
+    <definedName name="solver_opt" localSheetId="15" hidden="1">'6'!$F$6</definedName>
+    <definedName name="solver_opt" localSheetId="18" hidden="1">'7'!$E$7</definedName>
+    <definedName name="solver_opt" localSheetId="21" hidden="1">'8'!$E$6</definedName>
+    <definedName name="solver_opt" localSheetId="24" hidden="1">'9'!$F$8</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="6" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="9" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="12" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="15" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="18" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="21" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="24" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="18" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="24" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_rel1" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="6" hidden="1">3</definedName>
     <definedName name="solver_rel1" localSheetId="9" hidden="1">3</definedName>
     <definedName name="solver_rel1" localSheetId="12" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="15" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="18" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="21" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="24" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="6" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="18" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="24" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="9" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="18" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="24" hidden="1">3</definedName>
+    <definedName name="solver_rel4" localSheetId="18" hidden="1">3</definedName>
+    <definedName name="solver_rel4" localSheetId="24" hidden="1">3</definedName>
+    <definedName name="solver_rel5" localSheetId="18" hidden="1">1</definedName>
+    <definedName name="solver_rel5" localSheetId="24" hidden="1">1</definedName>
+    <definedName name="solver_rel6" localSheetId="18" hidden="1">3</definedName>
+    <definedName name="solver_rel6" localSheetId="24" hidden="1">1</definedName>
+    <definedName name="solver_rel7" localSheetId="18" hidden="1">1</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rhs1" localSheetId="3" hidden="1">'2'!$E$3:$E$5</definedName>
     <definedName name="solver_rhs1" localSheetId="6" hidden="1">0</definedName>
     <definedName name="solver_rhs1" localSheetId="9" hidden="1">0</definedName>
     <definedName name="solver_rhs1" localSheetId="12" hidden="1">0</definedName>
+    <definedName name="solver_rhs1" localSheetId="15" hidden="1">0</definedName>
+    <definedName name="solver_rhs1" localSheetId="18" hidden="1">20</definedName>
+    <definedName name="solver_rhs1" localSheetId="21" hidden="1">0</definedName>
+    <definedName name="solver_rhs1" localSheetId="24" hidden="1">1200</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">'1'!$E$3:$E$5</definedName>
     <definedName name="solver_rhs2" localSheetId="3" hidden="1">'2'!$E$3:$E$5</definedName>
     <definedName name="solver_rhs2" localSheetId="6" hidden="1">'3'!$J$3:$J$6</definedName>
     <definedName name="solver_rhs2" localSheetId="9" hidden="1">'4'!$F$3:$F$5</definedName>
     <definedName name="solver_rhs2" localSheetId="12" hidden="1">'5'!$G$3:$G$4</definedName>
+    <definedName name="solver_rhs2" localSheetId="15" hidden="1">'6'!$G$3:$G$5</definedName>
+    <definedName name="solver_rhs2" localSheetId="18" hidden="1">10</definedName>
+    <definedName name="solver_rhs2" localSheetId="21" hidden="1">'8'!$F$3:$F$5</definedName>
+    <definedName name="solver_rhs2" localSheetId="24" hidden="1">1000</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">'1'!$E$3:$E$5</definedName>
     <definedName name="solver_rhs3" localSheetId="3" hidden="1">'2'!$E$3:$E$5</definedName>
     <definedName name="solver_rhs3" localSheetId="9" hidden="1">'4'!$F$3:$F$5</definedName>
+    <definedName name="solver_rhs3" localSheetId="18" hidden="1">40</definedName>
+    <definedName name="solver_rhs3" localSheetId="24" hidden="1">1500</definedName>
+    <definedName name="solver_rhs4" localSheetId="18" hidden="1">20</definedName>
+    <definedName name="solver_rhs4" localSheetId="24" hidden="1">1200</definedName>
+    <definedName name="solver_rhs5" localSheetId="18" hidden="1">100</definedName>
+    <definedName name="solver_rhs5" localSheetId="24" hidden="1">'9'!$G$3:$G$6</definedName>
+    <definedName name="solver_rhs6" localSheetId="18" hidden="1">25</definedName>
+    <definedName name="solver_rhs6" localSheetId="24" hidden="1">'9'!$G$7</definedName>
+    <definedName name="solver_rhs7" localSheetId="18" hidden="1">'7'!$F$3:$F$6</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_rlx" localSheetId="15" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="18" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="21" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="24" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="6" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="9" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="12" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="15" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="18" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="21" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="24" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="6" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="12" hidden="1">2</definedName>
+    <definedName name="solver_scl" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="18" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="24" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="12" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="15" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="18" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="21" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="24" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="3" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="6" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="9" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="12" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="15" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="18" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="21" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="24" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="6" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="9" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="12" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="15" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="18" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="21" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="24" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="3" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="6" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="9" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="12" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="15" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="18" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="21" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="24" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="9" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="12" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="15" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="18" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="21" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="24" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="6" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="9" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="12" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="15" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="18" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="21" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="24" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_ver" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_ver" localSheetId="6" hidden="1">2</definedName>
     <definedName name="solver_ver" localSheetId="9" hidden="1">2</definedName>
     <definedName name="solver_ver" localSheetId="12" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="15" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="18" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="21" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="24" hidden="1">2</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -221,7 +388,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1155" uniqueCount="307">
   <si>
     <t>Ресурсы</t>
   </si>
@@ -815,6 +982,333 @@
   </si>
   <si>
     <t>$B$2:$E$2 &gt;= 0</t>
+  </si>
+  <si>
+    <t>Вещество</t>
+  </si>
+  <si>
+    <t>Сырье 1</t>
+  </si>
+  <si>
+    <t>Сырье 2</t>
+  </si>
+  <si>
+    <t>Сырье 3</t>
+  </si>
+  <si>
+    <t>Сырье 4</t>
+  </si>
+  <si>
+    <t>Итого в смеси</t>
+  </si>
+  <si>
+    <t>План (не менее)</t>
+  </si>
+  <si>
+    <t>Кол-во сырья (кг)</t>
+  </si>
+  <si>
+    <t>Вещество A</t>
+  </si>
+  <si>
+    <t>Вещество B</t>
+  </si>
+  <si>
+    <t>Вещество C</t>
+  </si>
+  <si>
+    <t>Лист: [2_Lab_Tables.xlsx]6</t>
+  </si>
+  <si>
+    <t>Отчет создан: 4/5/26 1:57:08 PM</t>
+  </si>
+  <si>
+    <t>Время решения: 196.985 секунд.</t>
+  </si>
+  <si>
+    <t>Число итераций: 3 Число подзадач: 0</t>
+  </si>
+  <si>
+    <t>Максимальное время Без пределов,  Число итераций Без пределов, Precision 1E-06, Использовать автоматическое масштабирование</t>
+  </si>
+  <si>
+    <t>$F$6</t>
+  </si>
+  <si>
+    <t>Цена (руб.) Итого в смеси</t>
+  </si>
+  <si>
+    <t>Кол-во сырья (кг) Сырье 1</t>
+  </si>
+  <si>
+    <t>Кол-во сырья (кг) Сырье 2</t>
+  </si>
+  <si>
+    <t>Кол-во сырья (кг) Сырье 3</t>
+  </si>
+  <si>
+    <t>Кол-во сырья (кг) Сырье 4</t>
+  </si>
+  <si>
+    <t>Вещество A Итого в смеси</t>
+  </si>
+  <si>
+    <t>Вещество B Итого в смеси</t>
+  </si>
+  <si>
+    <t>Вещество C Итого в смеси</t>
+  </si>
+  <si>
+    <t>$F$5&lt;=$G$5</t>
+  </si>
+  <si>
+    <t>$F$3:$F$5 &lt;= $G$3:$G$5</t>
+  </si>
+  <si>
+    <t>Изделие 1</t>
+  </si>
+  <si>
+    <t>Изделие 2</t>
+  </si>
+  <si>
+    <t>Изделие 3</t>
+  </si>
+  <si>
+    <t>Итого</t>
+  </si>
+  <si>
+    <t>Лимит / План</t>
+  </si>
+  <si>
+    <t>Оборудование 1 типа</t>
+  </si>
+  <si>
+    <t>Оборудование 2 типа</t>
+  </si>
+  <si>
+    <t>Сырье 1 вида</t>
+  </si>
+  <si>
+    <t>Сырье 2 вида</t>
+  </si>
+  <si>
+    <t>Общая стоимость (руб.)</t>
+  </si>
+  <si>
+    <t>Лист: [2_Lab_Tables.xlsx]7</t>
+  </si>
+  <si>
+    <t>Отчет создан: 4/5/26 2:06:29 PM</t>
+  </si>
+  <si>
+    <t>Время решения: 242.944 секунд.</t>
+  </si>
+  <si>
+    <t>$E$7</t>
+  </si>
+  <si>
+    <t>Общая стоимость (руб.) Итого</t>
+  </si>
+  <si>
+    <t>План производства (шт) Изделие 1</t>
+  </si>
+  <si>
+    <t>План производства (шт) Изделие 2</t>
+  </si>
+  <si>
+    <t>План производства (шт) Изделие 3</t>
+  </si>
+  <si>
+    <t>Оборудование 1 типа Итого</t>
+  </si>
+  <si>
+    <t>Оборудование 2 типа Итого</t>
+  </si>
+  <si>
+    <t>Сырье 1 вида Итого</t>
+  </si>
+  <si>
+    <t>Сырье 2 вида Итого</t>
+  </si>
+  <si>
+    <t>$E$6&lt;=$F$6</t>
+  </si>
+  <si>
+    <t>$B$2&lt;=20</t>
+  </si>
+  <si>
+    <t>$B$2&gt;=10</t>
+  </si>
+  <si>
+    <t>$C$2&lt;=40</t>
+  </si>
+  <si>
+    <t>$C$2&gt;=20</t>
+  </si>
+  <si>
+    <t>$D$2&lt;=100</t>
+  </si>
+  <si>
+    <t>$D$2&gt;=25</t>
+  </si>
+  <si>
+    <t>$E$3:$E$6 &lt;= $F$3:$F$6</t>
+  </si>
+  <si>
+    <t>Отчет создан: 4/5/26 2:06:30 PM</t>
+  </si>
+  <si>
+    <t>Ресурс</t>
+  </si>
+  <si>
+    <t>«Италия»</t>
+  </si>
+  <si>
+    <t>«Австрия»</t>
+  </si>
+  <si>
+    <t>«Скандинавия»</t>
+  </si>
+  <si>
+    <t>Кол-во альбомов (шт)</t>
+  </si>
+  <si>
+    <t>Финансы (руб.)</t>
+  </si>
+  <si>
+    <t>Бумага (лист.)</t>
+  </si>
+  <si>
+    <t>Трудозатраты (чел.-час.)</t>
+  </si>
+  <si>
+    <t>Лист: [2_Lab_Tables.xlsx]8</t>
+  </si>
+  <si>
+    <t>Отчет создан: 4/5/26 2:20:59 PM</t>
+  </si>
+  <si>
+    <t>Время решения: 190.967 секунд.</t>
+  </si>
+  <si>
+    <t>Прибыль (руб.) Итого</t>
+  </si>
+  <si>
+    <t>Кол-во альбомов (шт) «Италия»</t>
+  </si>
+  <si>
+    <t>Кол-во альбомов (шт) «Австрия»</t>
+  </si>
+  <si>
+    <t>Кол-во альбомов (шт) «Скандинавия»</t>
+  </si>
+  <si>
+    <t>Финансы (руб.) Итого</t>
+  </si>
+  <si>
+    <t>Бумага (лист.) Итого</t>
+  </si>
+  <si>
+    <t>Трудозатраты (чел.-час.) Итого</t>
+  </si>
+  <si>
+    <t>Лимитирующие ресурсы</t>
+  </si>
+  <si>
+    <t>Группа 1</t>
+  </si>
+  <si>
+    <t>Группа 2</t>
+  </si>
+  <si>
+    <t>Группа 3</t>
+  </si>
+  <si>
+    <t>Группа 4</t>
+  </si>
+  <si>
+    <t>Объем ресурса</t>
+  </si>
+  <si>
+    <t>План товарооборота (шт)</t>
+  </si>
+  <si>
+    <t>Складские площади ($м^2$)</t>
+  </si>
+  <si>
+    <t>Трудовые ресурсы (чел.-час.)</t>
+  </si>
+  <si>
+    <t>Издержки обращения (руб.)</t>
+  </si>
+  <si>
+    <t>Товарные запасы (руб.)</t>
+  </si>
+  <si>
+    <t>План товарооборота (руб.)</t>
+  </si>
+  <si>
+    <t>Лист: [2_Lab_Tables.xlsx]9</t>
+  </si>
+  <si>
+    <t>Отчет создан: 4/5/26 2:27:35 PM</t>
+  </si>
+  <si>
+    <t>Время решения: 260.154 секунд.</t>
+  </si>
+  <si>
+    <t>$F$8</t>
+  </si>
+  <si>
+    <t>План товарооборота (шт) Группа 1</t>
+  </si>
+  <si>
+    <t>План товарооборота (шт) Группа 2</t>
+  </si>
+  <si>
+    <t>План товарооборота (шт) Группа 3</t>
+  </si>
+  <si>
+    <t>План товарооборота (шт) Группа 4</t>
+  </si>
+  <si>
+    <t>Складские площади ($м^2$) Использовано</t>
+  </si>
+  <si>
+    <t>Трудовые ресурсы (чел.-час.) Использовано</t>
+  </si>
+  <si>
+    <t>Издержки обращения (руб.) Использовано</t>
+  </si>
+  <si>
+    <t>Товарные запасы (руб.) Использовано</t>
+  </si>
+  <si>
+    <t>$F$6&lt;=$G$6</t>
+  </si>
+  <si>
+    <t>$F$7</t>
+  </si>
+  <si>
+    <t>План товарооборота (руб.) Использовано</t>
+  </si>
+  <si>
+    <t>$F$7&lt;=$G$7</t>
+  </si>
+  <si>
+    <t>$B$2&gt;=1200</t>
+  </si>
+  <si>
+    <t>$C$2&gt;=1000</t>
+  </si>
+  <si>
+    <t>$D$2&gt;=1500</t>
+  </si>
+  <si>
+    <t>$E$2&gt;=1200</t>
+  </si>
+  <si>
+    <t>$F$3:$F$6 &lt;= $G$3:$G$6</t>
   </si>
 </sst>
 </file>
@@ -945,7 +1439,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -984,6 +1478,30 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3029,6 +3547,1061 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BE77A80-79B7-7C41-9D52-B2152A5E3B90}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="14">
+        <v>15.000000000000002</v>
+      </c>
+      <c r="C2" s="14">
+        <v>4.5</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A3" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="14">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14">
+        <v>1</v>
+      </c>
+      <c r="D3" s="14">
+        <v>0</v>
+      </c>
+      <c r="E3" s="14">
+        <v>4</v>
+      </c>
+      <c r="F3" s="14">
+        <f>SUMPRODUCT($B$2:$E$2,B3:E3)</f>
+        <v>19.5</v>
+      </c>
+      <c r="G3" s="14">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A4" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="14">
+        <v>2</v>
+      </c>
+      <c r="C4" s="14">
+        <v>0</v>
+      </c>
+      <c r="D4" s="14">
+        <v>3</v>
+      </c>
+      <c r="E4" s="14">
+        <v>5</v>
+      </c>
+      <c r="F4" s="14">
+        <f>SUMPRODUCT($B$2:$E$2,B4:E4)</f>
+        <v>30.000000000000004</v>
+      </c>
+      <c r="G4" s="14">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A5" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="14">
+        <v>1</v>
+      </c>
+      <c r="C5" s="14">
+        <v>2</v>
+      </c>
+      <c r="D5" s="14">
+        <v>4</v>
+      </c>
+      <c r="E5" s="14">
+        <v>6</v>
+      </c>
+      <c r="F5" s="14">
+        <f>SUMPRODUCT($B$2:$E$2,B5:E5)</f>
+        <v>24</v>
+      </c>
+      <c r="G5" s="14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A6" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="14">
+        <v>50</v>
+      </c>
+      <c r="C6" s="14">
+        <v>60</v>
+      </c>
+      <c r="D6" s="14">
+        <v>70</v>
+      </c>
+      <c r="E6" s="14">
+        <v>40</v>
+      </c>
+      <c r="F6" s="14">
+        <f>SUMPRODUCT($B$2:$E$2,B6:E6)</f>
+        <v>1020.0000000000001</v>
+      </c>
+      <c r="G6" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65A6FA78-A112-104F-98A7-606DFC1B3B03}">
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5"/>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5"/>
+      <c r="B7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5"/>
+      <c r="B8" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" s="22">
+        <v>0</v>
+      </c>
+      <c r="E16" s="22">
+        <v>1020.0000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+    </row>
+    <row r="22" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="D22" s="23">
+        <v>0</v>
+      </c>
+      <c r="E22" s="23">
+        <v>15.000000000000002</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="D23" s="23">
+        <v>0</v>
+      </c>
+      <c r="E23" s="23">
+        <v>4.5</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="D24" s="23">
+        <v>0</v>
+      </c>
+      <c r="E24" s="23">
+        <v>0</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D25" s="22">
+        <v>0</v>
+      </c>
+      <c r="E25" s="22">
+        <v>0</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="20"/>
+    </row>
+    <row r="29" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B31" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+    </row>
+    <row r="32" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="D32" s="23">
+        <v>19.5</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="21">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="D33" s="23">
+        <v>30.000000000000004</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="D34" s="23">
+        <v>24</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G34" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B36" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C36" s="21"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+    </row>
+    <row r="37" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="D37" s="23">
+        <v>15.000000000000002</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G37" s="23">
+        <v>15.000000000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="D38" s="23">
+        <v>4.5</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" s="23">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="D39" s="23">
+        <v>0</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G39" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D40" s="22">
+        <v>0</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G40" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="24"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB313CB-531F-6B4F-86C3-1FE50B396E0C}">
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B9" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+    </row>
+    <row r="10" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="D10" s="21">
+        <v>15.000000000000002</v>
+      </c>
+      <c r="E10" s="21">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21">
+        <v>50</v>
+      </c>
+      <c r="G10" s="21">
+        <v>1E+30</v>
+      </c>
+      <c r="H10" s="21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="21">
+        <v>4.5</v>
+      </c>
+      <c r="E11" s="21">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21">
+        <v>60</v>
+      </c>
+      <c r="G11" s="21">
+        <v>40</v>
+      </c>
+      <c r="H11" s="21">
+        <v>59.999999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="D12" s="21">
+        <v>0</v>
+      </c>
+      <c r="E12" s="21">
+        <v>-80</v>
+      </c>
+      <c r="F12" s="21">
+        <v>70</v>
+      </c>
+      <c r="G12" s="21">
+        <v>80</v>
+      </c>
+      <c r="H12" s="21">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D13" s="18">
+        <v>0</v>
+      </c>
+      <c r="E13" s="18">
+        <v>-190</v>
+      </c>
+      <c r="F13" s="18">
+        <v>40</v>
+      </c>
+      <c r="G13" s="18">
+        <v>190</v>
+      </c>
+      <c r="H13" s="18">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+    </row>
+    <row r="16" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B19" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+    </row>
+    <row r="20" spans="2:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="D20" s="21">
+        <v>19.5</v>
+      </c>
+      <c r="E20" s="21">
+        <v>0</v>
+      </c>
+      <c r="F20" s="21">
+        <v>26</v>
+      </c>
+      <c r="G20" s="21">
+        <v>1E+30</v>
+      </c>
+      <c r="H20" s="21">
+        <v>6.4999999999999982</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="D21" s="21">
+        <v>30.000000000000004</v>
+      </c>
+      <c r="E21" s="21">
+        <v>10</v>
+      </c>
+      <c r="F21" s="21">
+        <v>30</v>
+      </c>
+      <c r="G21" s="21">
+        <v>18</v>
+      </c>
+      <c r="H21" s="21">
+        <v>30.000000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="D22" s="18">
+        <v>24</v>
+      </c>
+      <c r="E22" s="18">
+        <v>29.999999999999996</v>
+      </c>
+      <c r="F22" s="18">
+        <v>24</v>
+      </c>
+      <c r="G22" s="18">
+        <v>12.999999999999996</v>
+      </c>
+      <c r="H22" s="18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96C87BC2-4EFD-AF4B-9877-B408C98C94F3}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="14">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14">
+        <v>33</v>
+      </c>
+      <c r="D2" s="14">
+        <v>45</v>
+      </c>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+    </row>
+    <row r="3" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A3" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="14">
+        <v>2</v>
+      </c>
+      <c r="C3" s="14">
+        <v>0</v>
+      </c>
+      <c r="D3" s="14">
+        <v>4</v>
+      </c>
+      <c r="E3" s="14">
+        <f>SUMPRODUCT(B2:D2,B3:D3)</f>
+        <v>200</v>
+      </c>
+      <c r="F3" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="B4" s="14">
+        <v>4</v>
+      </c>
+      <c r="C4" s="14">
+        <v>3</v>
+      </c>
+      <c r="D4" s="14">
+        <v>1</v>
+      </c>
+      <c r="E4" s="14">
+        <f>SUMPRODUCT(B2:D2,B4:D4)</f>
+        <v>184</v>
+      </c>
+      <c r="F4" s="14">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="14">
+        <v>10</v>
+      </c>
+      <c r="C5" s="14">
+        <v>15</v>
+      </c>
+      <c r="D5" s="14">
+        <v>20</v>
+      </c>
+      <c r="E5" s="14">
+        <f>SUMPRODUCT(B2:D2,B5:D5)</f>
+        <v>1495</v>
+      </c>
+      <c r="F5" s="14">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B6" s="14">
+        <v>30</v>
+      </c>
+      <c r="C6" s="14">
+        <v>20</v>
+      </c>
+      <c r="D6" s="14">
+        <v>25</v>
+      </c>
+      <c r="E6" s="14">
+        <f>SUMPRODUCT(B2:D2,B6:D6)</f>
+        <v>2085</v>
+      </c>
+      <c r="F6" s="14">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A7" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="B7" s="14">
+        <v>100</v>
+      </c>
+      <c r="C7" s="14">
+        <v>150</v>
+      </c>
+      <c r="D7" s="14">
+        <v>200</v>
+      </c>
+      <c r="E7" s="14">
+        <f>SUMPRODUCT(B2:D2,B7:D7)</f>
+        <v>14950</v>
+      </c>
+      <c r="F7" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE6B530-00F9-D84D-8351-A2E0D3F7B5C1}">
   <dimension ref="A1:H19"/>
@@ -3280,6 +4853,2619 @@
       </c>
     </row>
     <row r="19" spans="2:8" collapsed="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F44A3EB-01AF-0E47-92C7-BD95A8131E79}">
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5"/>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5"/>
+      <c r="B7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5"/>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="D16" s="22">
+        <v>0</v>
+      </c>
+      <c r="E16" s="22">
+        <v>14950</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+    </row>
+    <row r="22" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="23">
+        <v>0</v>
+      </c>
+      <c r="E22" s="23">
+        <v>10</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D23" s="23">
+        <v>0</v>
+      </c>
+      <c r="E23" s="23">
+        <v>33</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="D24" s="22">
+        <v>0</v>
+      </c>
+      <c r="E24" s="22">
+        <v>45</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="20"/>
+    </row>
+    <row r="28" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+    </row>
+    <row r="31" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="D31" s="23">
+        <v>200</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G31" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="D32" s="23">
+        <v>184</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="21">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="D33" s="23">
+        <v>1495</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="D34" s="23">
+        <v>2085</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="21">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B36" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="D36" s="23">
+        <v>10</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G36" s="21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B37" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="D37" s="23">
+        <v>10</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G37" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B38" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D38" s="23">
+        <v>33</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" s="21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B39" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D39" s="23">
+        <v>33</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" s="23">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B40" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="D40" s="23">
+        <v>45</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="21">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="D41" s="22">
+        <v>45</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="22">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6E0772-C749-C84B-AF82-54F1E2105C3F}">
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B9" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+    </row>
+    <row r="10" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="D10" s="21">
+        <v>10</v>
+      </c>
+      <c r="E10" s="21">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21">
+        <v>100</v>
+      </c>
+      <c r="G10" s="21">
+        <v>0</v>
+      </c>
+      <c r="H10" s="21">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D11" s="21">
+        <v>33</v>
+      </c>
+      <c r="E11" s="21">
+        <v>0</v>
+      </c>
+      <c r="F11" s="21">
+        <v>150</v>
+      </c>
+      <c r="G11" s="21">
+        <v>8.3266726846886741E-15</v>
+      </c>
+      <c r="H11" s="21">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" s="18">
+        <v>45</v>
+      </c>
+      <c r="E12" s="18">
+        <v>0</v>
+      </c>
+      <c r="F12" s="18">
+        <v>200</v>
+      </c>
+      <c r="G12" s="18">
+        <v>1E+30</v>
+      </c>
+      <c r="H12" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+    </row>
+    <row r="15" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B18" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+    </row>
+    <row r="19" spans="2:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="D19" s="21">
+        <v>200</v>
+      </c>
+      <c r="E19" s="21">
+        <v>2.7755575615628914E-15</v>
+      </c>
+      <c r="F19" s="21">
+        <v>200</v>
+      </c>
+      <c r="G19" s="21">
+        <v>39</v>
+      </c>
+      <c r="H19" s="21">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" s="21">
+        <v>184</v>
+      </c>
+      <c r="E20" s="21">
+        <v>0</v>
+      </c>
+      <c r="F20" s="21">
+        <v>500</v>
+      </c>
+      <c r="G20" s="21">
+        <v>1E+30</v>
+      </c>
+      <c r="H20" s="21">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="D21" s="21">
+        <v>1495</v>
+      </c>
+      <c r="E21" s="21">
+        <v>10</v>
+      </c>
+      <c r="F21" s="21">
+        <v>1495</v>
+      </c>
+      <c r="G21" s="21">
+        <v>105</v>
+      </c>
+      <c r="H21" s="21">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="D22" s="18">
+        <v>2085</v>
+      </c>
+      <c r="E22" s="18">
+        <v>0</v>
+      </c>
+      <c r="F22" s="18">
+        <v>4500</v>
+      </c>
+      <c r="G22" s="18">
+        <v>1E+30</v>
+      </c>
+      <c r="H22" s="18">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91369037-F2F5-F142-AE2A-2A85FBE25E91}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2" s="14">
+        <v>2200</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0</v>
+      </c>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+    </row>
+    <row r="3" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A3" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="B3" s="14">
+        <v>2</v>
+      </c>
+      <c r="C3" s="14">
+        <v>1</v>
+      </c>
+      <c r="D3" s="14">
+        <v>4</v>
+      </c>
+      <c r="E3" s="14">
+        <f>SUMPRODUCT(B2:D2,B3:D3)</f>
+        <v>4400</v>
+      </c>
+      <c r="F3" s="14">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A4" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4" s="14">
+        <v>4</v>
+      </c>
+      <c r="C4" s="14">
+        <v>2</v>
+      </c>
+      <c r="D4" s="14">
+        <v>2</v>
+      </c>
+      <c r="E4" s="14">
+        <f>SUMPRODUCT(B2:D2,B4:D4)</f>
+        <v>8800</v>
+      </c>
+      <c r="F4" s="14">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="B5" s="14">
+        <v>1</v>
+      </c>
+      <c r="C5" s="14">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14">
+        <v>2</v>
+      </c>
+      <c r="E5" s="14">
+        <f>SUMPRODUCT(B2:D2,B5:D5)</f>
+        <v>2200</v>
+      </c>
+      <c r="F5" s="14">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="20" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="14">
+        <v>220</v>
+      </c>
+      <c r="C6" s="14">
+        <v>180</v>
+      </c>
+      <c r="D6" s="14">
+        <v>300</v>
+      </c>
+      <c r="E6" s="14">
+        <f>SUMPRODUCT(B2:D2,B6:D6)</f>
+        <v>484000</v>
+      </c>
+      <c r="F6" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0228280-0137-B64A-933C-9D85221A37A7}">
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5"/>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5"/>
+      <c r="B7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5"/>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="D16" s="22">
+        <v>0</v>
+      </c>
+      <c r="E16" s="22">
+        <v>484000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+    </row>
+    <row r="22" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="D22" s="23">
+        <v>0</v>
+      </c>
+      <c r="E22" s="23">
+        <v>2200</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="D23" s="23">
+        <v>0</v>
+      </c>
+      <c r="E23" s="23">
+        <v>0</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="D24" s="22">
+        <v>0</v>
+      </c>
+      <c r="E24" s="22">
+        <v>0</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="20"/>
+    </row>
+    <row r="28" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+    </row>
+    <row r="31" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="D31" s="23">
+        <v>4400</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="21">
+        <v>31600</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="D32" s="23">
+        <v>8800</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="21">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="D33" s="23">
+        <v>2200</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B35" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35" s="21"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+    </row>
+    <row r="36" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="D36" s="23">
+        <v>2200</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G36" s="23">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="D37" s="23">
+        <v>0</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G37" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="D38" s="22">
+        <v>0</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G38" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="24"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5216E938-2AA0-C34E-B06A-44D4F30AC215}">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B9" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+    </row>
+    <row r="10" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10" s="21">
+        <v>2200</v>
+      </c>
+      <c r="E10" s="21">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21">
+        <v>220</v>
+      </c>
+      <c r="G10" s="21">
+        <v>1E+30</v>
+      </c>
+      <c r="H10" s="21">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="D11" s="21">
+        <v>0</v>
+      </c>
+      <c r="E11" s="21">
+        <v>-40</v>
+      </c>
+      <c r="F11" s="21">
+        <v>180</v>
+      </c>
+      <c r="G11" s="21">
+        <v>40</v>
+      </c>
+      <c r="H11" s="21">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="D12" s="18">
+        <v>0</v>
+      </c>
+      <c r="E12" s="18">
+        <v>-140</v>
+      </c>
+      <c r="F12" s="18">
+        <v>300</v>
+      </c>
+      <c r="G12" s="18">
+        <v>140</v>
+      </c>
+      <c r="H12" s="18">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+    </row>
+    <row r="15" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B18" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+    </row>
+    <row r="19" spans="2:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="D19" s="21">
+        <v>4400</v>
+      </c>
+      <c r="E19" s="21">
+        <v>0</v>
+      </c>
+      <c r="F19" s="21">
+        <v>36000</v>
+      </c>
+      <c r="G19" s="21">
+        <v>1E+30</v>
+      </c>
+      <c r="H19" s="21">
+        <v>31600</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="D20" s="21">
+        <v>8800</v>
+      </c>
+      <c r="E20" s="21">
+        <v>0</v>
+      </c>
+      <c r="F20" s="21">
+        <v>52000</v>
+      </c>
+      <c r="G20" s="21">
+        <v>1E+30</v>
+      </c>
+      <c r="H20" s="21">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="D21" s="18">
+        <v>2200</v>
+      </c>
+      <c r="E21" s="18">
+        <v>220</v>
+      </c>
+      <c r="F21" s="18">
+        <v>2200</v>
+      </c>
+      <c r="G21" s="18">
+        <v>10800</v>
+      </c>
+      <c r="H21" s="18">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B61C6F-C3CC-1349-B3CF-180EFCB332DB}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="B2" s="14">
+        <v>1200</v>
+      </c>
+      <c r="C2" s="14">
+        <v>1000</v>
+      </c>
+      <c r="D2" s="14">
+        <v>1500</v>
+      </c>
+      <c r="E2" s="14">
+        <v>2100</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A3" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="B3" s="14">
+        <v>18</v>
+      </c>
+      <c r="C3" s="14">
+        <v>26</v>
+      </c>
+      <c r="D3" s="14">
+        <v>16</v>
+      </c>
+      <c r="E3" s="14">
+        <v>10</v>
+      </c>
+      <c r="F3" s="14">
+        <f>SUMPRODUCT(B2:E2,B3:E3)</f>
+        <v>92600</v>
+      </c>
+      <c r="G3" s="14">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A4" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" s="14">
+        <v>150</v>
+      </c>
+      <c r="C4" s="14">
+        <v>140</v>
+      </c>
+      <c r="D4" s="14">
+        <v>50</v>
+      </c>
+      <c r="E4" s="14">
+        <v>80</v>
+      </c>
+      <c r="F4" s="14">
+        <f>SUMPRODUCT(B2:E2,B4:E4)</f>
+        <v>563000</v>
+      </c>
+      <c r="G4" s="14">
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A5" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="B5" s="14">
+        <v>170</v>
+      </c>
+      <c r="C5" s="14">
+        <v>230</v>
+      </c>
+      <c r="D5" s="14">
+        <v>280</v>
+      </c>
+      <c r="E5" s="14">
+        <v>120</v>
+      </c>
+      <c r="F5" s="14">
+        <f>SUMPRODUCT(B2:E2,B5:E5)</f>
+        <v>1106000</v>
+      </c>
+      <c r="G5" s="14">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A6" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" s="14">
+        <v>31</v>
+      </c>
+      <c r="C6" s="14">
+        <v>42</v>
+      </c>
+      <c r="D6" s="14">
+        <v>30</v>
+      </c>
+      <c r="E6" s="14">
+        <v>20</v>
+      </c>
+      <c r="F6" s="14">
+        <f>SUMPRODUCT(B2:E2,B6:E6)</f>
+        <v>166200</v>
+      </c>
+      <c r="G6" s="14">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A7" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" s="14">
+        <v>200</v>
+      </c>
+      <c r="C7" s="14">
+        <v>150</v>
+      </c>
+      <c r="D7" s="14">
+        <v>170</v>
+      </c>
+      <c r="E7" s="14">
+        <v>50</v>
+      </c>
+      <c r="F7" s="14">
+        <f>SUMPRODUCT(B2:E2,B7:E7)</f>
+        <v>750000</v>
+      </c>
+      <c r="G7" s="14">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="20" x14ac:dyDescent="0.2">
+      <c r="A8" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14">
+        <v>120</v>
+      </c>
+      <c r="C8" s="14">
+        <v>50</v>
+      </c>
+      <c r="D8" s="14">
+        <v>30</v>
+      </c>
+      <c r="E8" s="14">
+        <v>100</v>
+      </c>
+      <c r="F8" s="14">
+        <f>SUMPRODUCT(B2:E2,B8:E8)</f>
+        <v>449000</v>
+      </c>
+      <c r="G8" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7331B0BD-2A9C-DB48-9C3E-CF3104BA8C0D}">
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5"/>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5"/>
+      <c r="B7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5"/>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="22">
+        <v>359000</v>
+      </c>
+      <c r="E16" s="22">
+        <v>449000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+    </row>
+    <row r="22" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D22" s="23">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="23">
+        <v>1200</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="D23" s="23">
+        <v>1000</v>
+      </c>
+      <c r="E23" s="23">
+        <v>1000</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="D24" s="23">
+        <v>1500</v>
+      </c>
+      <c r="E24" s="23">
+        <v>1500</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="D25" s="22">
+        <v>1200</v>
+      </c>
+      <c r="E25" s="22">
+        <v>2100</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="20"/>
+    </row>
+    <row r="29" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B31" s="26" t="s">
+        <v>306</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+    </row>
+    <row r="32" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="D32" s="23">
+        <v>92600</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="21">
+        <v>17400</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="D33" s="23">
+        <v>563000</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" s="21">
+        <v>387000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="D34" s="23">
+        <v>1106000</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="21">
+        <v>94000</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="D35" s="23">
+        <v>166200</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="21">
+        <v>13800</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B37" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="D37" s="23">
+        <v>750000</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G37" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B38" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D38" s="23">
+        <v>1200</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G38" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B39" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="D39" s="23">
+        <v>1000</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G39" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B40" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="D40" s="23">
+        <v>1500</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G40" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="D41" s="22">
+        <v>2100</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" s="22">
+        <v>900</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD200FCF-3A54-A648-9B68-18A1C79CDE11}">
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B9" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+    </row>
+    <row r="10" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D10" s="21">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="21">
+        <v>-280</v>
+      </c>
+      <c r="F10" s="21">
+        <v>120</v>
+      </c>
+      <c r="G10" s="21">
+        <v>280</v>
+      </c>
+      <c r="H10" s="21">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="D11" s="21">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="21">
+        <v>-250</v>
+      </c>
+      <c r="F11" s="21">
+        <v>50</v>
+      </c>
+      <c r="G11" s="21">
+        <v>250</v>
+      </c>
+      <c r="H11" s="21">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="D12" s="21">
+        <v>1500</v>
+      </c>
+      <c r="E12" s="21">
+        <v>-310</v>
+      </c>
+      <c r="F12" s="21">
+        <v>30</v>
+      </c>
+      <c r="G12" s="21">
+        <v>310</v>
+      </c>
+      <c r="H12" s="21">
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="D13" s="18">
+        <v>2100</v>
+      </c>
+      <c r="E13" s="18">
+        <v>0</v>
+      </c>
+      <c r="F13" s="18">
+        <v>100</v>
+      </c>
+      <c r="G13" s="18">
+        <v>1E+30</v>
+      </c>
+      <c r="H13" s="18">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+    </row>
+    <row r="16" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B19" s="26" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+    </row>
+    <row r="20" spans="2:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="D20" s="21">
+        <v>92600</v>
+      </c>
+      <c r="E20" s="21">
+        <v>0</v>
+      </c>
+      <c r="F20" s="21">
+        <v>110000</v>
+      </c>
+      <c r="G20" s="21">
+        <v>1E+30</v>
+      </c>
+      <c r="H20" s="21">
+        <v>17400</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="D21" s="21">
+        <v>563000</v>
+      </c>
+      <c r="E21" s="21">
+        <v>0</v>
+      </c>
+      <c r="F21" s="21">
+        <v>950000</v>
+      </c>
+      <c r="G21" s="21">
+        <v>1E+30</v>
+      </c>
+      <c r="H21" s="21">
+        <v>387000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="D22" s="21">
+        <v>1106000</v>
+      </c>
+      <c r="E22" s="21">
+        <v>0</v>
+      </c>
+      <c r="F22" s="21">
+        <v>1200000</v>
+      </c>
+      <c r="G22" s="21">
+        <v>1E+30</v>
+      </c>
+      <c r="H22" s="21">
+        <v>94000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="D23" s="21">
+        <v>166200</v>
+      </c>
+      <c r="E23" s="21">
+        <v>0</v>
+      </c>
+      <c r="F23" s="21">
+        <v>180000</v>
+      </c>
+      <c r="G23" s="21">
+        <v>1E+30</v>
+      </c>
+      <c r="H23" s="21">
+        <v>13800</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+    </row>
+    <row r="25" spans="2:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="D25" s="18">
+        <v>750000</v>
+      </c>
+      <c r="E25" s="18">
+        <v>2</v>
+      </c>
+      <c r="F25" s="18">
+        <v>750000</v>
+      </c>
+      <c r="G25" s="18">
+        <v>34500</v>
+      </c>
+      <c r="H25" s="18">
+        <v>45000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
